--- a/config/fetter.xlsx
+++ b/config/fetter.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>最初の仲間</t>
+          <t>第一个伙伴</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>意気投合</t>
+          <t>意气相投</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>毒草の理</t>
+          <t>毒草之理</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>最初の仲間</t>
+          <t>第一个伙伴</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>頼れる相棒</t>
+          <t>可靠的伙伴</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>燃える友情</t>
+          <t>燃烧的友谊</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>最初の仲間</t>
+          <t>第一个伙伴</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>輝きの絆</t>
+          <t>光辉的纽带</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>波の共鳴</t>
+          <t>波的共鸣</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>一致団結</t>
+          <t>团结一致</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>協力連盟</t>
+          <t>合作联盟</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>奇術の持ち主</t>
+          <t>魔术的主人</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>意気投合</t>
+          <t>意气相投</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>頼れる相棒</t>
+          <t>可靠的伙伴</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>水の契約</t>
+          <t>水的契约</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>意気投合</t>
+          <t>意气相投</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>輝きの絆</t>
+          <t>光辉的纽带</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>岩石の契約</t>
+          <t>岩石契约</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>頼れる相棒</t>
+          <t>可靠的伙伴</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>輝きの絆</t>
+          <t>光辉的纽带</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>意思疎通</t>
+          <t>意思沟通</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>協力連盟</t>
+          <t>合作联盟</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>雷核覚醒</t>
+          <t>雷核觉醒</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>意思疎通</t>
+          <t>意思沟通</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>怒涛の荒波</t>
+          <t>怒涛巨浪</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>意思疎通</t>
+          <t>意思沟通</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>水の契約</t>
+          <t>水的契约</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>ギルドの頭</t>
+          <t>公会的头目</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>暗黙の同盟</t>
+          <t>默契的同盟</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>一致団結</t>
+          <t>团结一致</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>ギルドの頭</t>
+          <t>公会的头目</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>仲間の友情</t>
+          <t>伙伴的友谊</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>ギルドの頭</t>
+          <t>公会的头目</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>大切な絆</t>
+          <t>重要的纽带</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>岩石の契約</t>
+          <t>岩石契约</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>一致団結</t>
+          <t>团结一致</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>雷鳴の意志</t>
+          <t>雷鸣的意志</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>仲間の友情</t>
+          <t>伙伴的友谊</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>信頼の仲間</t>
+          <t>信赖的伙伴</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>奇跡の魔法</t>
+          <t>奇迹的魔法</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>仲間の友情</t>
+          <t>伙伴的友谊</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>魔法の輝き</t>
+          <t>魔法光芒</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>大地の契約</t>
+          <t>大地的契约</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>鉄壁の守護者</t>
+          <t>铁壁守护者</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>大切な絆</t>
+          <t>重要的纽带</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>信頼の仲間</t>
+          <t>信赖的伙伴</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>大切な絆</t>
+          <t>重要的纽带</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>暗黙の同盟</t>
+          <t>默契的同盟</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>戦場の友人</t>
+          <t>战场的好友</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>暗黙の同盟</t>
+          <t>默契的同盟</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>信頼の仲間</t>
+          <t>信赖的伙伴</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>雷の契約</t>
+          <t>闪电契约</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>自然の理</t>
+          <t>自然之理</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>自然の生霊</t>
+          <t>自然的灵魂</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>空の繋ぎ手</t>
+          <t>天空的纽带</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>深森の仲</t>
+          <t>深森之交</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>神聖な絆</t>
+          <t>神圣的纽带</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>対極の契り</t>
+          <t>对立的契约</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>自然の流れ</t>
+          <t>自然潮流</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>森林の絆</t>
+          <t>森林纽带</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>奇跡の魔法</t>
+          <t>奇迹的魔法</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>燃える友情</t>
+          <t>燃烧的友谊</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>対極の契り</t>
+          <t>对立的契约</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>自然の理</t>
+          <t>自然之理</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>大地の祝福</t>
+          <t>大地的祝福</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>森の守護者</t>
+          <t>森林守护者</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>大地の祝福</t>
+          <t>大地的祝福</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>深森の仲</t>
+          <t>深森之交</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>鉄壁結界</t>
+          <t>铁壁结界</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>自然の理</t>
+          <t>自然之理</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>自然の生霊</t>
+          <t>自然的灵魂</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>雷核覚醒</t>
+          <t>雷核觉醒</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>大地の祝福</t>
+          <t>大地的祝福</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>森林の絆</t>
+          <t>森林纽带</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>燃える友情</t>
+          <t>燃烧的友谊</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>自然の生霊</t>
+          <t>自然的灵魂</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>森林の絆</t>
+          <t>森林纽带</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>自然の流れ</t>
+          <t>自然潮流</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>空の繋ぎ手</t>
+          <t>天空的纽带</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>戦場の友人</t>
+          <t>战场的好友</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>自然の流れ</t>
+          <t>自然潮流</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>深森の仲</t>
+          <t>深森之交</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>神聖な心</t>
+          <t>神圣的心</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>神理を仰ぐ絆</t>
+          <t>敬仰神理的羁绊</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>神秘な力</t>
+          <t>神秘力量</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>森の守護者</t>
+          <t>森林守护者</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>神理を仰ぐ絆</t>
+          <t>敬仰神理的羁绊</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>信仰の心</t>
+          <t>信仰之心</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>固い友情</t>
+          <t>牢固的友谊</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>神理を仰ぐ絆</t>
+          <t>敬仰神理的羁绊</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>信仰深き者</t>
+          <t>信仰深厚的人</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>魔法の輝き</t>
+          <t>魔法光芒</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>神聖同盟</t>
+          <t>神圣同盟</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>神秘な力</t>
+          <t>神秘力量</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>固い友情</t>
+          <t>牢固的友谊</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>神聖同盟</t>
+          <t>神圣同盟</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>信仰の心</t>
+          <t>信仰之心</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>信仰の証</t>
+          <t>信仰的证明</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>神聖同盟</t>
+          <t>神圣同盟</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>信仰深き者</t>
+          <t>信仰深厚的人</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>翡翠の絆</t>
+          <t>翡翠的羁绊</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>魔法の申し子</t>
+          <t>魔法之子</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>信仰の心</t>
+          <t>信仰之心</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>吹雪の絆</t>
+          <t>吹雪的羁绊</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>魔法の申し子</t>
+          <t>魔法之子</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>神秘な力</t>
+          <t>神秘力量</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>毒草の理</t>
+          <t>毒草之理</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>魔法の申し子</t>
+          <t>魔法之子</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>信仰深き者</t>
+          <t>信仰深厚的人</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>信仰の心</t>
+          <t>信仰之心</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>空の旅人</t>
+          <t>天空旅行者</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>奇術の持ち主</t>
+          <t>魔术的主人</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>信仰の心</t>
+          <t>信仰之心</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>信仰の心</t>
+          <t>信仰之心</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>信仰の証</t>
+          <t>信仰的证明</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>神聖な心</t>
+          <t>神圣的心</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>研究管理員</t>
+          <t>研究管理人员</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>電力研究者</t>
+          <t>电力研究人员</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>研究管理員</t>
+          <t>研究管理人员</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>夢の旅人</t>
+          <t>梦之旅人</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>氷の契約</t>
+          <t>冰之契约</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>研究管理員</t>
+          <t>研究管理人员</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>探検の心</t>
+          <t>探索之心</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>鉄壁結界</t>
+          <t>铁壁结界</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>研究者の道</t>
+          <t>研究者之路</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>雷鳴の意志</t>
+          <t>雷鸣的意志</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>研究者の道</t>
+          <t>研究者之路</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>夢の旅人</t>
+          <t>梦之旅人</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>森の守護者</t>
+          <t>森林守护者</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>研究者の道</t>
+          <t>研究者之路</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>雷の契約</t>
+          <t>闪电契约</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>機械人間</t>
+          <t>机械人</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>研究の先</t>
+          <t>研究的方向</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>空の繋ぎ手</t>
+          <t>天空的纽带</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>機械人間</t>
+          <t>机械人</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>探検の心</t>
+          <t>探索之心</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>固い友情</t>
+          <t>牢固的友谊</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>機械人間</t>
+          <t>机械人</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>夢の旅人</t>
+          <t>梦之旅人</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>波の共鳴</t>
+          <t>波的共鸣</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>科学者の道</t>
+          <t>科学家之路</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>探検の心</t>
+          <t>探索之心</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>電力研究者</t>
+          <t>电力研究人员</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>科学者の道</t>
+          <t>科学家之路</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>科学者の道</t>
+          <t>科学家之路</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>研究の先</t>
+          <t>研究的方向</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>雷の契約</t>
+          <t>闪电契约</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>学園生活</t>
+          <t>校园生活</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>共鳴の序章</t>
+          <t>共鸣序章</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>学園生活</t>
+          <t>校园生活</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>学園の絆</t>
+          <t>学园的羁绊</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>毒の使者</t>
+          <t>毒使者</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>学園生活</t>
+          <t>校园生活</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>青春の安らぎ</t>
+          <t>青春的安宁</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>友情の証</t>
+          <t>友谊的证明</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>共鳴の序章</t>
+          <t>共鸣序章</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>友情の証</t>
+          <t>友谊的证明</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>学園の絆</t>
+          <t>学园的羁绊</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>水の使い手</t>
+          <t>水的使用者</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>友情の証</t>
+          <t>友谊的证明</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>青春の安らぎ</t>
+          <t>青春的安宁</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>青春謳歌</t>
+          <t>青春讴歌</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>共鳴の序章</t>
+          <t>共鸣序章</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>固い友情</t>
+          <t>牢固的友谊</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>青春謳歌</t>
+          <t>青春讴歌</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>学園の絆</t>
+          <t>学园的羁绊</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>翡翠の絆</t>
+          <t>翡翠的羁绊</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>青春謳歌</t>
+          <t>青春讴歌</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>青春の安らぎ</t>
+          <t>青春的安宁</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>岩石の契約</t>
+          <t>岩石契约</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>鉄壁の守護者</t>
+          <t>铁壁守护者</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>大地の契約</t>
+          <t>大地的契约</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>海風の絆</t>
+          <t>海风的羁绊</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>果てなき航路</t>
+          <t>没有尽头的航线</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>固い友情</t>
+          <t>牢固的友谊</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>海風の絆</t>
+          <t>海风的羁绊</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>遠征の海路</t>
+          <t>远征的海路</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>神聖な絆</t>
+          <t>神圣的纽带</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>海風の絆</t>
+          <t>海风的羁绊</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>波の共鳴</t>
+          <t>波的共鸣</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>怒涛の荒波</t>
+          <t>怒涛巨浪</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>海を目指す者</t>
+          <t>向大海进发的人</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>果てなき航路</t>
+          <t>没有尽头的航线</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>水の使い手</t>
+          <t>水的使用者</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>海を目指す者</t>
+          <t>向大海进发的人</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>遠征の海路</t>
+          <t>远征的海路</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>毒の使者</t>
+          <t>毒使者</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>海を目指す者</t>
+          <t>向大海进发的人</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>神聖な絆</t>
+          <t>神圣的纽带</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>信仰の証</t>
+          <t>信仰的证明</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>漂流の絆</t>
+          <t>漂流的羁绊</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>果てなき航路</t>
+          <t>没有尽头的航线</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>奇術の持ち主</t>
+          <t>魔术的主人</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>漂流の絆</t>
+          <t>漂流的羁绊</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>遠征の海路</t>
+          <t>远征的海路</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>水の使い手</t>
+          <t>水的使用者</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>極寒の絆</t>
+          <t>极寒的羁绊</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>氷川の絆</t>
+          <t>冰川之绊</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>鉄壁の守護者</t>
+          <t>铁壁守护者</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>極寒の絆</t>
+          <t>极寒的羁绊</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>吹雪の絆</t>
+          <t>吹雪的羁绊</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>氷と火</t>
+          <t>冰与火</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>極寒の絆</t>
+          <t>极寒的羁绊</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>氷の契約</t>
+          <t>冰之契约</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>氷川の絆</t>
+          <t>冰川之绊</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>空の旅人</t>
+          <t>天空旅行者</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>氷川の絆</t>
+          <t>冰川之绊</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>氷の契約</t>
+          <t>冰之契约</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>雪と火</t>
+          <t>雪与火</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>氷と火</t>
+          <t>冰与火</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>雪と火</t>
+          <t>雪与火</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>固い友情</t>
+          <t>牢固的友谊</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>機械ファミリー</t>
+          <t>机械家族</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>機械ファミリー</t>
+          <t>机械家族</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>機械ファミリー</t>
+          <t>机械家族</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
